--- a/results/sensitivity_analysis.xlsx
+++ b/results/sensitivity_analysis.xlsx
@@ -435,7 +435,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -451,7 +451,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -459,7 +459,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>n≥3 vs n≥5</t>
+          <t>n&gt;=3 vs n&gt;=5</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -509,7 +509,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>n≥10 vs n≥5</t>
+          <t>n&gt;=10 vs n&gt;=5</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,7 +522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>n≥15 vs n≥5</t>
+          <t>n&gt;=15 vs n&gt;=5</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -543,21 +543,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>vector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>spearman_rho</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -566,52 +571,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exponential vs current</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.9532</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{1,3,5}</t>
+        </is>
       </c>
       <c r="C2" t="n">
+        <v>0.9918</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>compressed vs current</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9903999999999999</v>
+          <t>convex</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{1,4,16}</t>
+        </is>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flat vs current</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9809</v>
+          <t>concave</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{1,5,6}</t>
+        </is>
       </c>
       <c r="C4" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>linear_high vs current</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.9903999999999999</v>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{2,3,4}</t>
+        </is>
       </c>
       <c r="C5" t="n">
+        <v>0.8501</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results/sensitivity_analysis.xlsx
+++ b/results/sensitivity_analysis.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="threshold_counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="threshold_correlation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="scale_correlation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="threshold_stability" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="top5_by_threshold" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="scale_correlation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,6 +430,16 @@
           <t>n_scenarios</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_incidents</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>incident_share_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -437,6 +448,12 @@
       <c r="B2" t="n">
         <v>104</v>
       </c>
+      <c r="C2" t="n">
+        <v>1921</v>
+      </c>
+      <c r="D2" t="n">
+        <v>94.40000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -445,6 +462,12 @@
       <c r="B3" t="n">
         <v>81</v>
       </c>
+      <c r="C3" t="n">
+        <v>1842</v>
+      </c>
+      <c r="D3" t="n">
+        <v>90.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -453,6 +476,12 @@
       <c r="B4" t="n">
         <v>41</v>
       </c>
+      <c r="C4" t="n">
+        <v>1581</v>
+      </c>
+      <c r="D4" t="n">
+        <v>77.69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -460,6 +489,12 @@
       </c>
       <c r="B5" t="n">
         <v>27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D5" t="n">
+        <v>69.58</v>
       </c>
     </row>
   </sheetData>
@@ -473,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,12 +519,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>spearman_rho</t>
+          <t>n_scenarios</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>p_value</t>
+          <t>shared_scenarios</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>top_k_overlap</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top_k_overlap_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>same_top_k_order</t>
         </is>
       </c>
     </row>
@@ -500,36 +550,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>n&gt;=10 vs n&gt;=5</t>
+          <t>n&gt;=5 vs n&gt;=5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>n&gt;=10 vs n&gt;=5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>n&gt;=15 vs n&gt;=5</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -543,6 +642,727 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_personal_data</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_special_categories</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>has_credentials</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LINDDUN categories</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AssetTech</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>baseline_risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>151</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2968058968058968</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2358722358722359</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>174</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08550368550368551</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>127</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06240786240786241</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>29</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.057002457002457</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>151</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2968058968058968</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2358722358722359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>174</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08550368550368551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>127</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.06240786240786241</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.057002457002457</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>151</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2968058968058968</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>120</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2358722358722359</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>174</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.08550368550368551</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>127</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.06240786240786241</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>29</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.057002457002457</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>151</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2968058968058968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>120</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2358722358722359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>174</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.08550368550368551</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Linkability, Identifiability</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>127</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.06240786240786241</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Unawareness, Non-compliance</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Software / Web Application</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>29</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.057002457002457</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -559,12 +1379,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>n_scenarios</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>spearman_rho</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>p_value</t>
         </is>
       </c>
     </row>
@@ -576,14 +1396,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1,3,5}</t>
+          <t>(1,3,5)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9918</v>
+        <v>194</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.9957</v>
       </c>
     </row>
     <row r="3">
@@ -594,14 +1414,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{1,4,16}</t>
+          <t>(1,4,16)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>194</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.9718</v>
       </c>
     </row>
     <row r="4">
@@ -612,14 +1432,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{1,5,6}</t>
+          <t>(1,5,6)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9969</v>
+        <v>194</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="5">
@@ -630,14 +1450,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{2,3,4}</t>
+          <t>(2,3,4)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8501</v>
+        <v>194</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.9191</v>
       </c>
     </row>
   </sheetData>
